--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484787_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484787_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.363200000000001</v>
+        <v>9.331300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9865</v>
+        <v>4.981</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3767</v>
+        <v>4.3503</v>
       </c>
       <c r="G2" t="n">
         <v>3.9153</v>
@@ -610,13 +610,13 @@
         <v>5.4723</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3262</v>
+        <v>-0.3582</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5749</v>
+        <v>-0.5804</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2487</v>
+        <v>0.2223</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.178</v>
+        <v>5.229</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9852</v>
+        <v>2.9399</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1928</v>
+        <v>2.2891</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8532999999999999</v>
+        <v>2.4041</v>
       </c>
       <c r="H3" t="n">
-        <v>1.094</v>
+        <v>-0.8883</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2408</v>
+        <v>3.2924</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7986</v>
+        <v>3.7538</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8923</v>
+        <v>0.3968</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9063</v>
+        <v>3.3571</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9453</v>
+        <v>-1.3497</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7982</v>
+        <v>-1.285</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1471</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4531</v>
+        <v>3.5853</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.2836</v>
+        <v>3.5853</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6454</v>
+        <v>-0.7604</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2438</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4016</v>
+        <v>0.0535</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7732</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6667</v>
+        <v>4.4729</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0372</v>
+        <v>2.5181</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6294</v>
+        <v>1.9547</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4511</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9055</v>
+        <v>1.094</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4544</v>
+        <v>-0.2408</v>
       </c>
       <c r="J4" t="n">
-        <v>1.607</v>
+        <v>2.7986</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3843</v>
+        <v>1.8923</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9913</v>
+        <v>0.9063</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.058</v>
+        <v>-1.9453</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5212</v>
+        <v>-0.7982</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5369</v>
+        <v>-1.1471</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3966</v>
+        <v>2.4531</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
         <v>5.2836</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7211</v>
+        <v>-0.0597</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3173</v>
+        <v>-0.2232</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4039</v>
+        <v>0.1635</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.7732</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2417</v>
+        <v>3.8192</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2965</v>
+        <v>0.2779</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9452</v>
+        <v>3.5413</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4041</v>
+        <v>-0.4511</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8883</v>
+        <v>-0.9055</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2924</v>
+        <v>0.4544</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7538</v>
+        <v>1.607</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3968</v>
+        <v>-0.3843</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3571</v>
+        <v>1.9913</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3497</v>
+        <v>-2.058</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.285</v>
+        <v>-0.5212</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.5369</v>
       </c>
       <c r="P5" t="n">
-        <v>3.5853</v>
+        <v>3.3966</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5853</v>
+        <v>5.2836</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7477</v>
+        <v>0.8736</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4574</v>
+        <v>0.5579</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2904</v>
+        <v>0.3157</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4769</v>
+        <v>0.4427</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1679</v>
+        <v>0.1828</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6448</v>
+        <v>0.2598</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2004</v>
+        <v>0.3084</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4102</v>
+        <v>-3.0623</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6106</v>
+        <v>3.3707</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7547</v>
+        <v>1.5551</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2398</v>
+        <v>-1.8587</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.485</v>
+        <v>3.4138</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9551</v>
+        <v>-1.2467</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8295</v>
+        <v>-1.2036</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1256</v>
+        <v>-0.0431</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>4.3401</v>
+        <v>2.8305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7336</v>
+        <v>-0.5075</v>
       </c>
       <c r="T6" t="n">
-        <v>0.606</v>
+        <v>-0.4288</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1276</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.566</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8678</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3539</v>
+        <v>0.4068</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3539</v>
+        <v>0.4068</v>
       </c>
       <c r="G7" t="n">
         <v>0.1299</v>
@@ -1000,13 +1000,13 @@
         <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0353</v>
+        <v>0.0882</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.3324</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0854</v>
+        <v>-0.2066</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0047</v>
+        <v>0.539</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3084</v>
+        <v>-0.2004</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0623</v>
+        <v>1.4102</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3707</v>
+        <v>-1.6106</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5551</v>
+        <v>1.7547</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8587</v>
+        <v>2.2398</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4138</v>
+        <v>-0.485</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2467</v>
+        <v>-1.9551</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2036</v>
+        <v>-0.8295</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0431</v>
+        <v>-1.1256</v>
       </c>
       <c r="P8" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8305</v>
+        <v>4.3401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8695000000000001</v>
+        <v>0.5891</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5262</v>
+        <v>0.5674</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3433</v>
+        <v>0.0218</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>-1.566</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5268</v>
+        <v>-0.5087</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3373</v>
+        <v>-0.2398</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1895</v>
+        <v>-0.2689</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0842</v>
@@ -1156,13 +1156,13 @@
         <v>0.5661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1764</v>
+        <v>-0.0789</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1111</v>
+        <v>0.0318</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.848</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.746</v>
+        <v>-3.7259</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9572</v>
+        <v>2.8778</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8947</v>
@@ -1234,13 +1234,13 @@
         <v>5.4723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2758</v>
+        <v>-0.2557</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3434</v>
+        <v>0.264</v>
       </c>
       <c r="V10" t="n">
         <v>-1.547</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>22.0455</v>
+        <v>22.67760000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1396</v>
+        <v>6.727399999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>15.9058</v>
+        <v>15.9499</v>
       </c>
       <c r="G11" t="n">
         <v>3.980599999999999</v>
@@ -1312,13 +1312,13 @@
         <v>33.0225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8056000000000001</v>
+        <v>-0.1738</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8436</v>
+        <v>-1.2557</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0379</v>
+        <v>1.0821</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8302</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3895</v>
+        <v>-0.2572</v>
       </c>
       <c r="E13" t="n">
         <v>-0.4821</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0925</v>
+        <v>0.2248</v>
       </c>
       <c r="G13" t="n">
         <v>1.3505</v>
@@ -1468,13 +1468,13 @@
         <v>0.1887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0417</v>
+        <v>0.0905</v>
       </c>
       <c r="T13" t="n">
         <v>0.1299</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1716</v>
+        <v>-0.0394</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6764</v>
+        <v>-0.4467</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4334</v>
+        <v>-0.3359</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2431</v>
+        <v>-0.1108</v>
       </c>
       <c r="G14" t="n">
         <v>1.0883</v>
@@ -1546,13 +1546,13 @@
         <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0664</v>
+        <v>0.1633</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0512</v>
+        <v>0.1834</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5483</v>
+        <v>-1.2152</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2719</v>
+        <v>-2.1745</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7236</v>
+        <v>0.9593</v>
       </c>
       <c r="G15" t="n">
         <v>1.462</v>
@@ -1624,13 +1624,13 @@
         <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1798</v>
+        <v>0.1533</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4115</v>
+        <v>-0.3141</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2317</v>
+        <v>0.4674</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7304</v>
+        <v>-1.7508</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6713</v>
+        <v>-1.7687</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0591</v>
+        <v>0.018</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7927999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1382</v>
+        <v>0.1178</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1488</v>
+        <v>-0.2462</v>
       </c>
       <c r="U16" t="n">
-        <v>0.287</v>
+        <v>0.364</v>
       </c>
       <c r="V16" t="n">
         <v>1.566</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8765</v>
+        <v>-2.0222</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.1182</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4819</v>
+        <v>-2.1403</v>
       </c>
       <c r="G17" t="n">
         <v>-2.9464</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4474</v>
+        <v>0.3017</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5008</v>
+        <v>0.0136</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0534</v>
+        <v>0.2881</v>
       </c>
       <c r="V17" t="n">
         <v>1.566</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.986</v>
+        <v>-2.9271</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2522</v>
+        <v>-1.3496</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7338</v>
+        <v>-1.5774</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1407</v>
@@ -1936,13 +1936,13 @@
         <v>1.6983</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2792</v>
+        <v>-0.2203</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1023</v>
+        <v>-0.1998</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1769</v>
+        <v>-0.0205</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2452</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3437</v>
+        <v>-5.399</v>
       </c>
       <c r="E20" t="n">
         <v>-4.3457</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.998</v>
+        <v>-1.0533</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3397</v>
@@ -2014,13 +2014,13 @@
         <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4492</v>
+        <v>0.3939</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2076</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6015</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9244</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0487</v>
+        <v>-5.9319</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1015</v>
+        <v>-4.6143</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9472</v>
+        <v>-1.3176</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1032</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3381</v>
+        <v>0.4549</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6808</v>
+        <v>-0.1936</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0188</v>
+        <v>0.6485</v>
       </c>
       <c r="V21" t="n">
         <v>1.8678</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-22.0453</v>
+        <v>-21.3959</v>
       </c>
       <c r="E22" t="n">
-        <v>-15.9059</v>
+        <v>-15.9057</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.139699999999999</v>
+        <v>-5.49</v>
       </c>
       <c r="G22" t="n">
         <v>-3.980800000000001</v>
@@ -2170,13 +2170,13 @@
         <v>11.322</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8058000000000001</v>
+        <v>1.4551</v>
       </c>
       <c r="T22" t="n">
         <v>-1.0379</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8436</v>
+        <v>2.493</v>
       </c>
       <c r="V22" t="n">
         <v>2.8302</v>
